--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488185_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488185_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2961</v>
+        <v>3.4416</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5783</v>
+        <v>1.9701</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7177</v>
+        <v>1.4715</v>
       </c>
       <c r="G2" t="n">
         <v>2.4339</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5471</v>
+        <v>0.6926</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0037</v>
+        <v>0.388</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.3046</v>
       </c>
       <c r="V2" t="n">
         <v>0.315</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0829</v>
+        <v>1.6845</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5145</v>
+        <v>1.6331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5685</v>
+        <v>0.0514</v>
       </c>
       <c r="G3" t="n">
         <v>0.1426</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9583</v>
+        <v>0.5599</v>
       </c>
       <c r="T3" t="n">
-        <v>1.302</v>
+        <v>0.4206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6563</v>
+        <v>0.1393</v>
       </c>
       <c r="V3" t="n">
         <v>-0.315</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6771</v>
+        <v>1.5021</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7923</v>
+        <v>2.4648</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1152</v>
+        <v>-0.9627</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3336</v>
+        <v>0.0891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3406</v>
+        <v>-1.4421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6742</v>
+        <v>1.5312</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2862</v>
+        <v>2.2349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1926</v>
+        <v>-0.3482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0936</v>
+        <v>2.5831</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6198</v>
+        <v>-2.1458</v>
       </c>
       <c r="N4" t="n">
-        <v>0.148</v>
+        <v>-1.0938</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7678</v>
+        <v>-1.052</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3987</v>
+        <v>0.1536</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2473</v>
+        <v>0.0827</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1514</v>
+        <v>0.0709</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3144</v>
+        <v>1.2594</v>
       </c>
       <c r="W4" t="n">
         <v>1.2589</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5733</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2077</v>
+        <v>0.967</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2689</v>
+        <v>2.1068</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0612</v>
+        <v>-1.1399</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0891</v>
+        <v>-0.3336</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4421</v>
+        <v>0.3406</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5312</v>
+        <v>-0.6742</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2349</v>
+        <v>0.2862</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3482</v>
+        <v>0.1926</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5831</v>
+        <v>0.0936</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1458</v>
+        <v>-0.6198</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0938</v>
+        <v>0.148</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.052</v>
+        <v>-0.7678</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1408</v>
+        <v>0.6886</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1131</v>
+        <v>0.5618</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0276</v>
+        <v>0.1268</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2594</v>
+        <v>-0.3144</v>
       </c>
       <c r="W5" t="n">
         <v>1.2589</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G6" t="n">
         <v>0.1306</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0579</v>
+        <v>-1.7624</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0563</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0016</v>
+        <v>-1.7061</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2282</v>
@@ -1000,13 +1000,13 @@
         <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2743</v>
+        <v>0.0211</v>
       </c>
       <c r="T7" t="n">
         <v>0.1567</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.431</v>
+        <v>-0.1356</v>
       </c>
       <c r="V7" t="n">
         <v>0.0005</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. FRISCIA PEREZ</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5888</v>
+        <v>-2.1507</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6564</v>
+        <v>-0.375</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9324</v>
+        <v>-1.7757</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4605</v>
+        <v>-1.1323</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8032</v>
+        <v>-1.7729</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6574</v>
+        <v>0.6405</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.547</v>
+        <v>0.5202</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5884</v>
+        <v>-0.2583</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>0.7785</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9136</v>
+        <v>-1.6525</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2147</v>
+        <v>-1.5145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6989</v>
+        <v>-0.138</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.24</v>
+        <v>-0.3895</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1094</v>
+        <v>-0.1159</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1306</v>
+        <v>-0.2736</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>U. FRISCIA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0097</v>
+        <v>-2.4909</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8647</v>
+        <v>-0.5585</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.145</v>
+        <v>-1.9324</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1323</v>
+        <v>-1.4605</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7729</v>
+        <v>-0.8032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6405</v>
+        <v>-0.6574</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5202</v>
+        <v>-0.547</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2583</v>
+        <v>-0.5884</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7785</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6525</v>
+        <v>-0.9136</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5145</v>
+        <v>-0.2147</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.138</v>
+        <v>-0.6989</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2485</v>
+        <v>-0.1421</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6056</v>
+        <v>-0.0115</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6429</v>
+        <v>-0.1306</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8877</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1566</v>
+        <v>-2.8622</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2903</v>
+        <v>-0.0944</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8663</v>
+        <v>-2.7678</v>
       </c>
       <c r="G10" t="n">
         <v>1.5189</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2509</v>
+        <v>0.5453</v>
       </c>
       <c r="T10" t="n">
-        <v>0.434</v>
+        <v>0.6299</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1831</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5177</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.248</v>
+        <v>-3.1506</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.399</v>
+        <v>-3.2031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.151</v>
+        <v>0.0525</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5098</v>
@@ -1312,13 +1312,13 @@
         <v>2.4087</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1321</v>
+        <v>0.2294</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0074</v>
+        <v>0.1884</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1395</v>
+        <v>0.041</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6502</v>
+        <v>-4.65</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8873</v>
+        <v>3.887500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.5375</v>
+        <v>-8.537599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3493</v>
@@ -1393,10 +1393,10 @@
         <v>2.3999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3008</v>
+        <v>2.3007</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09929999999999981</v>
+        <v>0.09919999999999993</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7744</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5094</v>
+        <v>6.7539</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0847</v>
+        <v>7.3785</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5753</v>
+        <v>-0.6246</v>
       </c>
       <c r="G13" t="n">
         <v>5.3615</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3698</v>
+        <v>-0.1253</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3867</v>
+        <v>-0.0929</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0169</v>
+        <v>-0.0324</v>
       </c>
       <c r="V13" t="n">
         <v>1.8883</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3332</v>
+        <v>4.1015</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7243</v>
+        <v>5.1574</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3911</v>
+        <v>-1.0559</v>
       </c>
       <c r="G14" t="n">
         <v>1.5971</v>
@@ -1546,13 +1546,13 @@
         <v>1.8529</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0685</v>
+        <v>0.8369</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2247</v>
+        <v>0.6579</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8438</v>
+        <v>0.179</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3043</v>
+        <v>0.3776</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6407</v>
+        <v>0.7387</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3364</v>
+        <v>-0.361</v>
       </c>
       <c r="G16" t="n">
         <v>1.9869</v>
@@ -1702,13 +1702,13 @@
         <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4417</v>
+        <v>-0.3684</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0584</v>
+        <v>0.0395</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3833</v>
+        <v>-0.4079</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1644</v>
+        <v>-0.4699</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5349</v>
+        <v>-0.6389</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6993</v>
+        <v>0.169</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2426</v>
+        <v>-1.0416</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3273</v>
+        <v>-0.5333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5699</v>
+        <v>-0.5083</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1526</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1852</v>
+        <v>-0.5884</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3378</v>
+        <v>0.0829</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.91</v>
+        <v>-0.5361</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1421</v>
+        <v>0.0552</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7678</v>
+        <v>-0.5913</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7411</v>
+        <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2791</v>
+        <v>-0.1694</v>
       </c>
       <c r="T17" t="n">
-        <v>1.736</v>
+        <v>-0.1334</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4569</v>
+        <v>-0.0361</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2254</v>
+        <v>-0.7288</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3451</v>
+        <v>-0.6827</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1197</v>
+        <v>-0.0461</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0416</v>
+        <v>-2.8974</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5333</v>
+        <v>-1.2923</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5083</v>
+        <v>-1.6051</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-1.558</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5884</v>
+        <v>-1.1125</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0829</v>
+        <v>-0.4455</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5361</v>
+        <v>-1.3394</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0552</v>
+        <v>-0.1798</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5913</v>
+        <v>-1.1596</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0751</v>
+        <v>-0.4222</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1604</v>
+        <v>-0.2331</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0853</v>
+        <v>-0.189</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5872</v>
+        <v>-1.3962</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2703</v>
+        <v>-1.4612</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.317</v>
+        <v>0.065</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8974</v>
+        <v>-1.4785</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2923</v>
+        <v>-0.9657</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6051</v>
+        <v>-0.5129</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.558</v>
+        <v>0.6264</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1125</v>
+        <v>0.3254</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4455</v>
+        <v>0.301</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3394</v>
+        <v>-2.1049</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1798</v>
+        <v>-1.2911</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1596</v>
+        <v>-0.8138</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4823</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2806</v>
+        <v>-0.5841</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8207</v>
+        <v>-0.3454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4599</v>
+        <v>-0.2388</v>
       </c>
       <c r="V19" t="n">
-        <v>3.1466</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>3.1466</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4688</v>
+        <v>-1.4145</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1941</v>
+        <v>-0.4107</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2747</v>
+        <v>-1.0038</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2806</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7059</v>
+        <v>-0.6516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9849</v>
+        <v>-0.2014</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.721</v>
+        <v>-0.4502</v>
       </c>
       <c r="V20" t="n">
         <v>0.6294</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6211</v>
+        <v>-1.7077</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5384</v>
+        <v>-0.8361</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0827</v>
+        <v>-0.8716</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4785</v>
+        <v>0.2426</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9657</v>
+        <v>-0.3273</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5129</v>
+        <v>0.5699</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6264</v>
+        <v>1.1526</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3254</v>
+        <v>-0.1852</v>
       </c>
       <c r="L21" t="n">
-        <v>0.301</v>
+        <v>1.3378</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1049</v>
+        <v>-0.91</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2911</v>
+        <v>-0.1421</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8138</v>
+        <v>-0.7678</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.7411</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.0382</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.297</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.1117</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.4087</v>
-      </c>
       <c r="S21" t="n">
-        <v>-1.8091</v>
+        <v>-0.2643</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4226</v>
+        <v>0.365</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3865</v>
+        <v>-0.6293</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.674</v>
+        <v>-2.11</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3434</v>
+        <v>-1.9517</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3306</v>
+        <v>-0.1583</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3848</v>
@@ -2170,13 +2170,13 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2157</v>
+        <v>-0.6516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5471</v>
+        <v>-0.1554</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6685</v>
+        <v>-0.4962</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.650100000000002</v>
+        <v>4.65</v>
       </c>
       <c r="E23" t="n">
-        <v>8.537400000000002</v>
+        <v>8.537399999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8874</v>
+        <v>-3.8873</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3493</v>
+        <v>2.349300000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9286000000000005</v>
+        <v>0.9286000000000008</v>
       </c>
       <c r="I23" t="n">
         <v>1.4205</v>
@@ -2236,10 +2236,10 @@
         <v>-4.6855</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.8369</v>
+        <v>-4.836900000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264000000000002</v>
+        <v>0.9264</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.0438</v>
@@ -2248,13 +2248,13 @@
         <v>12.97</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4001</v>
+        <v>-2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0993000000000005</v>
+        <v>-0.09919999999999998</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.3007</v>
+        <v>-2.3009</v>
       </c>
       <c r="V23" t="n">
         <v>3.7744</v>
